--- a/pdf2img/tabel/table_2.xlsx
+++ b/pdf2img/tabel/table_2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,6 +441,15 @@
       <c r="H1" t="n">
         <v>7</v>
       </c>
+      <c r="I1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -455,248 +464,306 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dasar,</t>
+          <t>Dasar,Kredit</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Kredit</t>
+          <t>(Prime</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(Prime</t>
+          <t>Lending</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lending</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
           <t>Rate)</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Tanggal</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tanggal</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+          <t>Suku</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bunga</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Dasar</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Kredit</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>(Prime</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lending</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rate)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>(%</t>
+          <t>Berdasarkan</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>tahun}</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>Segmen</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>per</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>Kredit</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kredit</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Kredit</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Kredit</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Suku</t>
+          <t>Kredit</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bunga</t>
+          <t>Ritel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dasar</t>
+          <t>Menegah™**</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kredit</t>
+          <t>Kegcil**</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(Prime</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Lending</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Rate)</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+          <t>Mikro**</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Berdasarkan</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Segmen</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bisnis</t>
-        </is>
-      </c>
+          <t>Korporasi</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Suku</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bunga</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Dasar</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>Kredit</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>10,10%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10,10%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>9,10%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12,10%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>13,20%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>10,60%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>13,60%</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kredit</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+          <t>(Primme</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Lending</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Rate)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kecil**</t>
+          <t>(%</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NMikra**</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>per</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>tahun},</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Suku</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Bunga</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dasar</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Kredit</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>(Prime</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Lending</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Rate)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
